--- a/data/trans_dic/IP31KM14_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP31KM14_2023-Clase-trans_dic.xlsx
@@ -496,12 +496,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,25; 26,24</t>
+          <t>10,65; 22,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12,69; 32,47</t>
+          <t>8,92; 20,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,93; 24,81</t>
+          <t>10,88; 20,14</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20,97%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,41; 24,91</t>
+          <t>13,34; 28,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>14,75; 29,34</t>
+          <t>11,35; 25,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,31; 24,31</t>
+          <t>14,7; 24,69</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>11,46; 31,95</t>
+          <t>8,91; 25,7</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,76; 26,09</t>
+          <t>11,6; 33,43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11,85; 25,47</t>
+          <t>12,48; 27,02</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>19,08%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,19; 19,8</t>
+          <t>15,4; 26,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,11; 26,08</t>
+          <t>12,98; 22,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,44; 21,43</t>
+          <t>15,5; 22,74</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,85%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>14,36; 27,43</t>
+          <t>13,1; 25,66</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>13,45; 26,88</t>
+          <t>15,08; 28,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,19; 24,75</t>
+          <t>15,42; 24,61</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16,87%</t>
+          <t>16,47%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,7; 35,58</t>
+          <t>4,56; 17,79</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 16,76</t>
+          <t>14,96; 33,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,76; 22,99</t>
+          <t>11,25; 22,74</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>18,14%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>14,71; 20,78</t>
+          <t>15,42; 21,08</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>15,52; 21,37</t>
+          <t>15,85; 21,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16,18; 20,52</t>
+          <t>16,33; 20,14</t>
         </is>
       </c>
     </row>
@@ -933,12 +933,12 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
           <t>Niña</t>
-        </is>
-      </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Niño</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1009,17 +1009,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>16244</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>25996</t>
+          <t>13973</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42240</t>
+          <t>33653</t>
         </is>
       </c>
     </row>
@@ -1032,17 +1032,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>10429; 26685</t>
+          <t>12909; 27834</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>17147; 43886</t>
+          <t>8949; 20998</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30628; 58770</t>
+          <t>24108; 44620</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>21</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1082,17 +1082,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>18637</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>19651</t>
+          <t>16813</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>35726</t>
+          <t>35450</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1105,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10659; 23265</t>
+          <t>11989; 25882</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>13820; 27490</t>
+          <t>10827; 24561</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>26776; 45482</t>
+          <t>27229; 45748</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20043</t>
+          <t>20067</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1178,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5743; 16006</t>
+          <t>4977; 14354</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5461; 16265</t>
+          <t>6033; 17388</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13327; 28635</t>
+          <t>13464; 29143</t>
         </is>
       </c>
     </row>
@@ -1205,12 +1205,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>45</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1228,17 +1228,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>31494</t>
+          <t>41231</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>30130</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>74169</t>
+          <t>71361</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1251,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19805; 42681</t>
+          <t>30390; 52666</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32142; 55466</t>
+          <t>22933; 40143</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>57562; 91772</t>
+          <t>57967; 85030</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23656</t>
+          <t>27366</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>30605</t>
+          <t>24446</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54261</t>
+          <t>51813</t>
         </is>
       </c>
     </row>
@@ -1324,17 +1324,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16583; 31679</t>
+          <t>19071; 37363</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21444; 42871</t>
+          <t>17414; 32969</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>41766; 68042</t>
+          <t>40242; 64237</t>
         </is>
       </c>
     </row>
@@ -1351,12 +1351,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>22</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1374,17 +1374,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>16791</t>
+          <t>6310</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>16119</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23265</t>
+          <t>22430</t>
         </is>
       </c>
     </row>
@@ -1397,17 +1397,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>11508; 24510</t>
+          <t>3005; 11719</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3031; 11569</t>
+          <t>10526; 23778</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16219; 31702</t>
+          <t>15328; 30980</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>157</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1447,17 +1447,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>114180</t>
+          <t>122578</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>135524</t>
+          <t>112195</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>249704</t>
+          <t>234773</t>
         </is>
       </c>
     </row>
@@ -1470,17 +1470,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>94890; 134072</t>
+          <t>104173; 142469</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>113642; 156541</t>
+          <t>96730; 130270</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>222911; 282677</t>
+          <t>210029; 259038</t>
         </is>
       </c>
     </row>
